--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="25">
   <si>
     <t>ID</t>
   </si>
@@ -83,6 +83,12 @@
   </si>
   <si>
     <t>Dawes Rolls Full Document - Creek By Blood - Page 632</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -414,15 +420,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O859"/>
+  <dimension ref="A1:Q859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
     <col min="12" max="12" width="12.7109375" customWidth="1"/>
     <col min="14" max="14" width="53.7109375" customWidth="1"/>
+    <col min="16" max="16" width="16.85546875" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -468,8 +476,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1900</v>
       </c>
@@ -486,7 +500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>1901</v>
@@ -506,7 +520,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>1902</v>
@@ -526,7 +540,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -546,7 +560,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -566,7 +580,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -586,7 +600,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -606,7 +620,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -626,7 +640,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -646,7 +660,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -666,7 +680,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -686,7 +700,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:17">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -706,7 +720,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:17">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -726,7 +740,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:17">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -746,7 +760,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:17">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>1914</v>

--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1739" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="27">
   <si>
     <t>ID</t>
   </si>
@@ -89,6 +89,12 @@
   </si>
   <si>
     <t>Image Binary</t>
+  </si>
+  <si>
+    <t>Stricken from roll</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
 </sst>
 </file>
@@ -15044,8 +15050,35 @@
         <f t="shared" si="38"/>
         <v>631</v>
       </c>
+      <c r="D730" t="s">
+        <v>25</v>
+      </c>
+      <c r="E730" t="s">
+        <v>26</v>
+      </c>
+      <c r="F730" t="s">
+        <v>26</v>
+      </c>
+      <c r="G730" t="s">
+        <v>26</v>
+      </c>
+      <c r="H730">
+        <v>-1</v>
+      </c>
+      <c r="I730" t="s">
+        <v>26</v>
+      </c>
+      <c r="J730" t="s">
+        <v>26</v>
+      </c>
+      <c r="K730" t="s">
+        <v>26</v>
+      </c>
       <c r="L730" t="s">
-        <v>16</v>
+        <v>26</v>
+      </c>
+      <c r="M730" t="s">
+        <v>26</v>
       </c>
       <c r="N730" t="str">
         <f t="shared" si="39"/>

--- a/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Seminole/Seminole Freedman.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1747" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1748" uniqueCount="28">
   <si>
     <t>ID</t>
   </si>
@@ -85,16 +85,19 @@
     <t>Dawes Rolls Full Document - Creek By Blood - Page 632</t>
   </si>
   <si>
-    <t>Image Name</t>
-  </si>
-  <si>
-    <t>Image Binary</t>
-  </si>
-  <si>
     <t>Stricken from roll</t>
   </si>
   <si>
     <t>N/A</t>
+  </si>
+  <si>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -426,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q859"/>
+  <dimension ref="A1:R859"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="12.85546875" customWidth="1"/>
@@ -434,9 +437,10 @@
     <col min="14" max="14" width="53.7109375" customWidth="1"/>
     <col min="16" max="16" width="16.85546875" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="21" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -483,13 +487,16 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Q1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+        <v>25</v>
+      </c>
+      <c r="R1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1900</v>
       </c>
@@ -506,7 +513,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>1901</v>
@@ -526,7 +533,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A67" si="0">A3+1</f>
         <v>1902</v>
@@ -546,7 +553,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>1903</v>
@@ -566,7 +573,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>1904</v>
@@ -586,7 +593,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>1905</v>
@@ -606,7 +613,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>1906</v>
@@ -626,7 +633,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>1907</v>
@@ -646,7 +653,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>1908</v>
@@ -666,7 +673,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>1909</v>
@@ -686,7 +693,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>1910</v>
@@ -706,7 +713,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:18">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>1911</v>
@@ -726,7 +733,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:18">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>1912</v>
@@ -746,7 +753,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:18">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>1913</v>
@@ -766,7 +773,7 @@
         <v>Dawes Rolls Full Document - Creek By Blood - Page 627</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:18">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>1914</v>
@@ -15051,34 +15058,34 @@
         <v>631</v>
       </c>
       <c r="D730" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H730">
         <v>-1</v>
       </c>
       <c r="I730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="K730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="M730" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="N730" t="str">
         <f t="shared" si="39"/>
